--- a/data/trans_camb/IP19C09-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP19C09-Provincia-trans_camb.xlsx
@@ -583,7 +583,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-19,55; 0,0</t>
+          <t>-20,51; 0,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-22,62; 0,0</t>
+          <t>-19,01; 0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,88; 8,75</t>
+          <t>-4,95; 8,5</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,05; 8,68</t>
+          <t>-5,34; 8,59</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-8,31; 3,4</t>
+          <t>-8,25; 3,2</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-8,64; 3,04</t>
+          <t>-8,06; 3,22</t>
         </is>
       </c>
     </row>
@@ -739,7 +739,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,2; 7,63</t>
+          <t>-2,21; 7,48</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 10,51</t>
+          <t>-0,53; 9,65</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,04; 3,53</t>
+          <t>-2,02; 3,99</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,03; 0,0</t>
+          <t>-5,0; 0,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,59; 4,1</t>
+          <t>-1,57; 3,41</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,07; 4,58</t>
+          <t>-1,22; 4,38</t>
         </is>
       </c>
     </row>
@@ -895,7 +895,7 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,19</t>
+          <t>0,0; 13,65</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,31</t>
+          <t>0,0; 9,78</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-10,34; 5,34</t>
+          <t>-9,45; 6,17</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-9,43; 5,15</t>
+          <t>-10,28; 4,77</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,81; 6,45</t>
+          <t>-3,5; 6,21</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-4,41; 4,28</t>
+          <t>-4,39; 4,53</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,34</t>
+          <t>0,0; 8,75</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,27; 14,98</t>
+          <t>1,28; 15,04</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-9,66; 0,0</t>
+          <t>-12,31; 0,0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,33; 11,13</t>
+          <t>-2,88; 11,7</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,13; 1,55</t>
+          <t>-3,19; 1,5</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,43; 9,78</t>
+          <t>0,54; 9,83</t>
         </is>
       </c>
     </row>
@@ -1255,17 +1255,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-15,63; 0,0</t>
+          <t>-17,26; 0,0</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-7,08; 17,11</t>
+          <t>-7,11; 19,0</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,81</t>
+          <t>0,0; 17,12</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -1275,12 +1275,12 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-4,29; 5,52</t>
+          <t>-4,57; 5,56</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-3,81; 9,15</t>
+          <t>-3,83; 9,59</t>
         </is>
       </c>
     </row>
@@ -1363,7 +1363,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-11,65; 4,35</t>
+          <t>-10,91; 4,23</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-12,58; 3,3</t>
+          <t>-11,44; 3,3</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-11,62; 0,0</t>
+          <t>-13,65; 0,0</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-4,93; 9,73</t>
+          <t>-5,24; 8,29</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-6,78; 2,16</t>
+          <t>-6,54; 2,0</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-5,13; 4,53</t>
+          <t>-5,32; 4,45</t>
         </is>
       </c>
     </row>
@@ -1519,7 +1519,7 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-3,44; 2,09</t>
+          <t>-3,39; 2,11</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-6,09; 0,0</t>
+          <t>-5,19; 0,0</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-6,67; 0,0</t>
+          <t>-6,71; 0,0</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-6,65; 0,0</t>
+          <t>-6,72; 0,0</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-3,49; 0,52</t>
+          <t>-3,41; 0,55</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-3,76; -0,48</t>
+          <t>-4,1; -0,48</t>
         </is>
       </c>
     </row>
@@ -1723,32 +1723,32 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-1,51; 4,69</t>
+          <t>-1,47; 4,01</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 5,89</t>
+          <t>-0,76; 5,54</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-8,78; 2,47</t>
+          <t>-8,93; 2,94</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-9,93; 1,66</t>
+          <t>-9,7; 1,6</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-4,26; 1,95</t>
+          <t>-4,32; 1,9</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-3,84; 2,41</t>
+          <t>-4,19; 2,13</t>
         </is>
       </c>
     </row>
@@ -1809,22 +1809,22 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-86,42; 110,76</t>
+          <t>-87,78; 103,44</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-90,16; 76,69</t>
+          <t>-89,93; 52,59</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-79,4; 103,68</t>
+          <t>-77,81; 102,66</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-73,95; 142,38</t>
+          <t>-74,1; 122,51</t>
         </is>
       </c>
     </row>
@@ -1879,32 +1879,32 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 1,79</t>
+          <t>-1,37; 1,94</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 3,06</t>
+          <t>-0,7; 3,03</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-3,14; 0,79</t>
+          <t>-3,02; 0,47</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-2,63; 1,56</t>
+          <t>-2,65; 1,38</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-1,69; 0,73</t>
+          <t>-1,74; 0,72</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 1,51</t>
+          <t>-1,03; 1,64</t>
         </is>
       </c>
     </row>
@@ -1955,32 +1955,32 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-62,92; 313,53</t>
+          <t>-65,09; 269,82</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-37,11; 454,94</t>
+          <t>-38,55; 417,3</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-76,29; 40,49</t>
+          <t>-78,16; 31,07</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-66,26; 83,44</t>
+          <t>-64,12; 72,04</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-60,39; 48,28</t>
+          <t>-60,11; 54,03</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-37,48; 94,41</t>
+          <t>-37,04; 103,19</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP19C09-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP19C09-Provincia-trans_camb.xlsx
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-20,51; 0,0</t>
+          <t>-19,79; 0,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-19,01; 0,0</t>
+          <t>-18,46; 0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,95; 8,5</t>
+          <t>-4,83; 10,06</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,34; 8,59</t>
+          <t>-6,77; 8,69</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-8,25; 3,2</t>
+          <t>-7,83; 3,54</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-8,06; 3,22</t>
+          <t>-7,38; 3,25</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,21; 7,48</t>
+          <t>-2,22; 6,29</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 9,65</t>
+          <t>-0,9; 10,33</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,02; 3,99</t>
+          <t>-2,01; 3,63</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,0; 0,0</t>
+          <t>-4,09; 0,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,57; 3,41</t>
+          <t>-1,56; 3,56</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 4,38</t>
+          <t>-1,14; 4,34</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,65</t>
+          <t>0,0; 13,76</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,78</t>
+          <t>0,0; 12,33</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-9,45; 6,17</t>
+          <t>-10,33; 6,18</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-10,28; 4,77</t>
+          <t>-10,37; 4,43</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,5; 6,21</t>
+          <t>-3,34; 6,93</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-4,39; 4,53</t>
+          <t>-4,39; 4,96</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,75</t>
+          <t>0,0; 8,38</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,28; 15,04</t>
+          <t>1,82; 15,17</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-12,31; 0,0</t>
+          <t>-9,71; 0,0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,88; 11,7</t>
+          <t>-2,81; 10,71</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,19; 1,5</t>
+          <t>-3,86; 1,53</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,54; 9,83</t>
+          <t>-0,07; 9,65</t>
         </is>
       </c>
     </row>
@@ -1255,17 +1255,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-17,26; 0,0</t>
+          <t>-15,94; 0,0</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-7,11; 19,0</t>
+          <t>-7,13; 16,25</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,12</t>
+          <t>0,0; 18,74</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -1275,12 +1275,12 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-4,57; 5,56</t>
+          <t>-5,64; 6,05</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-3,83; 9,59</t>
+          <t>-3,81; 9,77</t>
         </is>
       </c>
     </row>
@@ -1411,32 +1411,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-10,91; 4,23</t>
+          <t>-11,1; 4,24</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-11,44; 3,3</t>
+          <t>-11,33; 3,27</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-13,65; 0,0</t>
+          <t>-11,76; 0,0</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-5,24; 8,29</t>
+          <t>-5,43; 9,81</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-6,54; 2,0</t>
+          <t>-6,66; 1,16</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-5,32; 4,45</t>
+          <t>-5,07; 4,56</t>
         </is>
       </c>
     </row>
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-3,39; 2,11</t>
+          <t>-3,44; 2,13</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-5,19; 0,0</t>
+          <t>-5,93; 0,0</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-6,71; 0,0</t>
+          <t>-6,68; 0,0</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-6,72; 0,0</t>
+          <t>-6,58; 0,0</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-3,41; 0,55</t>
+          <t>-3,19; 0,86</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-4,1; -0,48</t>
+          <t>-3,98; -0,48</t>
         </is>
       </c>
     </row>
@@ -1723,32 +1723,32 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 4,01</t>
+          <t>-1,5; 3,96</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 5,54</t>
+          <t>-0,79; 5,38</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-8,93; 2,94</t>
+          <t>-9,7; 2,43</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-9,7; 1,6</t>
+          <t>-9,04; 1,6</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-4,32; 1,9</t>
+          <t>-4,26; 1,92</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-4,19; 2,13</t>
+          <t>-4,04; 2,41</t>
         </is>
       </c>
     </row>
@@ -1809,22 +1809,22 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-87,78; 103,44</t>
+          <t>-88,44; 106,44</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-89,93; 52,59</t>
+          <t>-89,62; 76,25</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-77,81; 102,66</t>
+          <t>-81,03; 102,05</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-74,1; 122,51</t>
+          <t>-75,83; 121,39</t>
         </is>
       </c>
     </row>
@@ -1879,32 +1879,32 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 1,94</t>
+          <t>-1,17; 1,85</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 3,03</t>
+          <t>-0,45; 2,9</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-3,02; 0,47</t>
+          <t>-3,15; 0,66</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-2,65; 1,38</t>
+          <t>-2,65; 1,35</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-1,74; 0,72</t>
+          <t>-1,78; 0,73</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-1,03; 1,64</t>
+          <t>-1,0; 1,5</t>
         </is>
       </c>
     </row>
@@ -1955,32 +1955,32 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-65,09; 269,82</t>
+          <t>-60,85; 267,64</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-38,55; 417,3</t>
+          <t>-35,38; 408,48</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-78,16; 31,07</t>
+          <t>-75,74; 42,4</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-64,12; 72,04</t>
+          <t>-65,43; 69,45</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-60,11; 54,03</t>
+          <t>-60,94; 48,64</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-37,04; 103,19</t>
+          <t>-36,1; 92,91</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP19C09-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP19C09-Provincia-trans_camb.xlsx
@@ -519,13 +519,13 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="F1" s="3" t="n"/>
@@ -593,22 +593,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0,42</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1,85</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>-6,47</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>-6,47</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0,42</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1,85</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-19,79; 0,0</t>
+          <t>-4,88; 8,75</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-18,46; 0,0</t>
+          <t>-5,05; 8,68</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,83; 10,06</t>
+          <t>-19,55; 0,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-6,77; 8,69</t>
+          <t>-22,62; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-7,83; 3,54</t>
+          <t>-8,31; 3,4</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-7,38; 3,25</t>
+          <t>-8,64; 3,04</t>
         </is>
       </c>
     </row>
@@ -669,22 +669,22 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>17,51%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>76,66%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>17,51%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>76,66%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -749,22 +749,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>0,15</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-1,0</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>0,78</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>3,3</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0,15</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-1,0</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,22; 6,29</t>
+          <t>-2,04; 3,53</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 10,33</t>
+          <t>-5,03; 0,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,01; 3,63</t>
+          <t>-2,2; 7,63</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,09; 0,0</t>
+          <t>-0,73; 10,51</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 3,56</t>
+          <t>-1,59; 4,1</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 4,34</t>
+          <t>-1,07; 4,58</t>
         </is>
       </c>
     </row>
@@ -825,22 +825,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>14,9%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>70,63%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>298,3%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>14,9%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -905,22 +905,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-2,48</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-2,85</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>4,4</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>2,39</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-2,48</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-2,85</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,76</t>
+          <t>-10,34; 5,34</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,33</t>
+          <t>-9,43; 5,15</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-10,33; 6,18</t>
+          <t>0,0; 15,19</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-10,37; 4,43</t>
+          <t>0,0; 12,31</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,34; 6,93</t>
+          <t>-3,81; 6,45</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-4,39; 4,96</t>
+          <t>-4,41; 4,28</t>
         </is>
       </c>
     </row>
@@ -981,22 +981,22 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-47,88%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-54,87%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>inf%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-47,88%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-54,87%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1061,22 +1061,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-1,97</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>3,22</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>1,51</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>5,7</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-1,97</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>3,22</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,38</t>
+          <t>-9,66; 0,0</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,82; 15,17</t>
+          <t>-2,33; 11,13</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-9,71; 0,0</t>
+          <t>0,0; 7,34</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,81; 10,71</t>
+          <t>1,27; 14,98</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,86; 1,53</t>
+          <t>-3,13; 1,55</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,07; 9,65</t>
+          <t>0,43; 9,78</t>
         </is>
       </c>
     </row>
@@ -1137,22 +1137,22 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>163,76%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>inf%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>163,76%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1217,22 +1217,22 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>5,33</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
           <t>-3,55</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>1,58</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>5,33</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-15,94; 0,0</t>
+          <t>0,0; 17,81</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-7,13; 16,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,74</t>
+          <t>-15,63; 0,0</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-7,08; 17,11</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-5,64; 6,05</t>
+          <t>-4,29; 5,52</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-3,81; 9,77</t>
+          <t>-3,81; 9,15</t>
         </is>
       </c>
     </row>
@@ -1293,22 +1293,22 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>44,55%</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1373,22 +1373,22 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>-2,33</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>1,74</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
           <t>-0,78</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>-1,25</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>-2,33</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>1,74</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-11,1; 4,24</t>
+          <t>-11,62; 0,0</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-11,33; 3,27</t>
+          <t>-4,93; 9,73</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-11,76; 0,0</t>
+          <t>-11,65; 4,35</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-5,43; 9,81</t>
+          <t>-12,58; 3,3</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-6,66; 1,16</t>
+          <t>-6,78; 2,16</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-5,07; 4,56</t>
+          <t>-5,13; 4,53</t>
         </is>
       </c>
     </row>
@@ -1449,22 +1449,22 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>74,79%</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
           <t>-26,99%</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>-43,16%</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>74,79%</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -1529,22 +1529,22 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>-1,9</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>-1,9</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
           <t>-0,08</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>-1,12</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>-1,9</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>-1,9</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-3,44; 2,13</t>
+          <t>-6,67; 0,0</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-5,93; 0,0</t>
+          <t>-6,65; 0,0</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-6,68; 0,0</t>
+          <t>-3,44; 2,09</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-6,58; 0,0</t>
+          <t>-6,09; 0,0</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-3,19; 0,86</t>
+          <t>-3,49; 0,52</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-3,98; -0,48</t>
+          <t>-3,76; -0,48</t>
         </is>
       </c>
     </row>
@@ -1605,17 +1605,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
           <t>-7,37%</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -1685,22 +1685,22 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
+          <t>-3,18</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>-3,64</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
           <t>0,81</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>1,72</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>-3,18</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>-3,64</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -1723,32 +1723,32 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 3,96</t>
+          <t>-8,78; 2,47</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 5,38</t>
+          <t>-9,93; 1,66</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-9,7; 2,43</t>
+          <t>-1,51; 4,69</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-9,04; 1,6</t>
+          <t>-0,75; 5,89</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-4,26; 1,92</t>
+          <t>-4,26; 1,95</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-4,04; 2,41</t>
+          <t>-3,84; 2,41</t>
         </is>
       </c>
     </row>
@@ -1761,22 +1761,22 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
+          <t>-45,53%</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>-52,06%</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
           <t>107,08%</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>226,95%</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>-45,53%</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>-52,06%</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -1799,32 +1799,32 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-86,42; 110,76</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-90,16; 76,69</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-88,44; 106,44</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-89,62; 76,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-81,03; 102,05</t>
+          <t>-79,4; 103,68</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-75,83; 121,39</t>
+          <t>-73,95; 142,38</t>
         </is>
       </c>
     </row>
@@ -1841,22 +1841,22 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
+          <t>-1,24</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>-0,65</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
           <t>0,24</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>1,15</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>-1,24</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>-0,65</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -1879,32 +1879,32 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 1,85</t>
+          <t>-3,14; 0,79</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 2,9</t>
+          <t>-2,63; 1,56</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-3,15; 0,66</t>
+          <t>-1,17; 1,79</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-2,65; 1,35</t>
+          <t>-0,49; 3,06</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-1,78; 0,73</t>
+          <t>-1,69; 0,73</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 1,5</t>
+          <t>-1,08; 1,51</t>
         </is>
       </c>
     </row>
@@ -1917,22 +1917,22 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
+          <t>-40,5%</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>-21,11%</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
           <t>16,93%</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>82,66%</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>-40,5%</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>-21,11%</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -1955,32 +1955,32 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-60,85; 267,64</t>
+          <t>-76,29; 40,49</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-35,38; 408,48</t>
+          <t>-66,26; 83,44</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-75,74; 42,4</t>
+          <t>-62,92; 313,53</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-65,43; 69,45</t>
+          <t>-37,11; 454,94</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-60,94; 48,64</t>
+          <t>-60,39; 48,28</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-36,1; 92,91</t>
+          <t>-37,48; 94,41</t>
         </is>
       </c>
     </row>
